--- a/COC04.xlsx
+++ b/COC04.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="196">
   <si>
     <t/>
   </si>
@@ -142,6 +142,12 @@
     <t>KITKAT 2F MLTPACK102</t>
   </si>
   <si>
+    <t>10036981</t>
+  </si>
+  <si>
+    <t>KIT KAT CHOCO 4F 35G</t>
+  </si>
+  <si>
     <t>10015698</t>
   </si>
   <si>
@@ -157,12 +163,6 @@
     <t>MILO CHOCO BAR 15G</t>
   </si>
   <si>
-    <t>10036981</t>
-  </si>
-  <si>
-    <t>KIT KAT CHOCO 4F 35G</t>
-  </si>
-  <si>
     <t>20046198</t>
   </si>
   <si>
@@ -253,21 +253,21 @@
     <t>KINDER JOY DC COMICS</t>
   </si>
   <si>
+    <t>20129814</t>
+  </si>
+  <si>
+    <t>MLKITA CNDY BTES 24G</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>20139949</t>
   </si>
   <si>
     <t>LMNILO CRNCHY CHO 18</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20129814</t>
-  </si>
-  <si>
-    <t>MLKITA CNDY BTES 24G</t>
-  </si>
-  <si>
     <t>20135665</t>
   </si>
   <si>
@@ -316,13 +316,25 @@
     <t>WNHAE GMMY MXD.FRT32</t>
   </si>
   <si>
+    <t>20143893</t>
+  </si>
+  <si>
+    <t>DARK WONDER CSW 2X40</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20142508</t>
+  </si>
+  <si>
+    <t>DARK WONDER  BDD2X40</t>
+  </si>
+  <si>
     <t>20117108</t>
   </si>
   <si>
-    <t>BENG-BENG PCK 3X20G</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>BENG-BENG PCK 3X20 G</t>
   </si>
   <si>
     <t>20044008</t>
@@ -388,6 +400,12 @@
     <t>FSHRMANS COLA 22</t>
   </si>
   <si>
+    <t>20115134</t>
+  </si>
+  <si>
+    <t>FSHRMAN'S CHO.ORG 25</t>
+  </si>
+  <si>
     <t>20132839</t>
   </si>
   <si>
@@ -481,21 +499,36 @@
     <t>MENTOS CND ROL AGR37</t>
   </si>
   <si>
-    <t>20115134</t>
-  </si>
-  <si>
-    <t>FSHRMAN'S CHO.ORG 25</t>
+    <t>20087289</t>
+  </si>
+  <si>
+    <t>CHP.CHUPS BITES 56G</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
+    <t>20139774</t>
+  </si>
+  <si>
+    <t>CH.CHUP ROPES S/C 24</t>
+  </si>
+  <si>
+    <t>20144098</t>
+  </si>
+  <si>
+    <t>C/CHUPS CRZY DIPS 14</t>
+  </si>
+  <si>
     <t>20115133</t>
   </si>
   <si>
     <t>FSHRMAN'S CHO.MINT22</t>
   </si>
   <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>10035320</t>
   </si>
   <si>
@@ -505,37 +538,34 @@
     <t>RT,(E-4B)</t>
   </si>
   <si>
+    <t>10035319</t>
+  </si>
+  <si>
+    <t>STRPSILS H.LMN 6S/8S</t>
+  </si>
+  <si>
+    <t>20001380</t>
+  </si>
+  <si>
+    <t>STRPSILS VIT.C 6S/8S</t>
+  </si>
+  <si>
+    <t>20027910</t>
+  </si>
+  <si>
+    <t>STRPSIL LMN&amp;HR 6S/8S</t>
+  </si>
+  <si>
     <t>10035551</t>
   </si>
   <si>
     <t>STREPSILS REG 6S/8S</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20001380</t>
-  </si>
-  <si>
-    <t>STRPSILS VIT.C 6S/8S</t>
-  </si>
-  <si>
-    <t>10035319</t>
-  </si>
-  <si>
-    <t>STRPSILS H.LMN 6S/8S</t>
-  </si>
-  <si>
     <t>20090773</t>
   </si>
   <si>
     <t>STRPSILS EX.STRG 8'S</t>
-  </si>
-  <si>
-    <t>20027910</t>
-  </si>
-  <si>
-    <t>STRPSIL LMN&amp;HR 6S/8S</t>
   </si>
   <si>
     <t>20012951</t>
@@ -961,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1343,10 +1373,10 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -1354,19 +1384,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -1383,10 +1413,10 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1403,10 +1433,10 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1423,10 +1453,10 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1666,7 +1696,7 @@
         <v>82</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -1686,7 +1716,7 @@
         <v>82</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -1706,7 +1736,7 @@
         <v>82</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -1726,7 +1756,7 @@
         <v>82</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>89</v>
@@ -1923,10 +1953,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -1934,19 +1964,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -1954,19 +1984,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="E50" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -1983,10 +2013,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2003,10 +2033,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2023,10 +2053,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2043,10 +2073,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2063,73 +2093,73 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="E58" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2143,13 +2173,13 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2163,30 +2193,30 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2194,19 +2224,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2214,19 +2244,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="C63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="E63" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2243,10 +2273,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2263,10 +2293,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2274,19 +2304,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2294,19 +2324,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2314,19 +2344,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="C68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2343,10 +2373,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2354,19 +2384,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2374,122 +2404,122 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>163</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>163</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>163</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>163</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="E75" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>163</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2503,92 +2533,192 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>5</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>5</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>5</v>
+        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>5</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="E81" s="1" t="s">
+      <c r="B82" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F86" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/COC04.xlsx
+++ b/COC04.xlsx
@@ -109,7 +109,7 @@
     <t>10003485</t>
   </si>
   <si>
-    <t>S/Q CHOCO ALMOND 52G</t>
+    <t>S/Q CHOCO ALMND 52 G</t>
   </si>
   <si>
     <t>5</t>
@@ -118,7 +118,7 @@
     <t>10036987</t>
   </si>
   <si>
-    <t>S/Q CHOCO CASHEW 52G</t>
+    <t>S/Q CHOCO CASHW 52 G</t>
   </si>
   <si>
     <t>20140016</t>

--- a/COC04.xlsx
+++ b/COC04.xlsx
@@ -91,7 +91,7 @@
     <t>10010192</t>
   </si>
   <si>
-    <t>S/Q CHOCO CASHEW 22G</t>
+    <t>SQ CHOCO CASHEW 22 G</t>
   </si>
   <si>
     <t>10038880</t>

--- a/COC04.xlsx
+++ b/COC04.xlsx
@@ -85,7 +85,7 @@
     <t>20095888</t>
   </si>
   <si>
-    <t>S/Q CHUNKY WHT 82G</t>
+    <t>S/Q CHUNKY WHT 82 G</t>
   </si>
   <si>
     <t>10010192</t>
@@ -103,7 +103,7 @@
     <t>20022908</t>
   </si>
   <si>
-    <t>S/Q CHUNKY ALMOND 82</t>
+    <t>S/Q CHUNKY ALMD 82 G</t>
   </si>
   <si>
     <t>10003485</t>
@@ -238,7 +238,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
+    <t>RT,(E-0.5B)</t>
   </si>
   <si>
     <t>20057442</t>
@@ -999,7 +999,7 @@
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="4" customWidth="1"/>
     <col min="5" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2256,7 +2256,7 @@
         <v>144</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2276,7 +2276,7 @@
         <v>144</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2296,7 +2296,7 @@
         <v>144</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2316,7 +2316,7 @@
         <v>144</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2336,7 +2336,7 @@
         <v>144</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
